--- a/InputData/fuels/FoVTStCT/Fraction of Vehicle Types Subject to Carbon Tax.xlsx
+++ b/InputData/fuels/FoVTStCT/Fraction of Vehicle Types Subject to Carbon Tax.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\fuels\FoVTStCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBDA14F-08DC-403F-A891-09BD1A08308D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5DDC02-9FE4-455D-8946-020E6D28104C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="1140" windowWidth="19180" windowHeight="5820" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
+    <workbookView xWindow="8520" yWindow="2835" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -714,7 +714,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE28"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.26953125" customWidth="1"/>
@@ -722,102 +722,105 @@
     <col min="3" max="3" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="5">
         <v>2021</v>
       </c>
-      <c r="C1" s="5">
+      <c r="D1" s="5">
         <v>2022</v>
       </c>
-      <c r="D1" s="5">
+      <c r="E1" s="5">
         <v>2023</v>
       </c>
-      <c r="E1" s="5">
+      <c r="F1" s="5">
         <v>2024</v>
       </c>
-      <c r="F1" s="5">
+      <c r="G1" s="5">
         <v>2025</v>
       </c>
-      <c r="G1" s="5">
+      <c r="H1" s="5">
         <v>2026</v>
       </c>
-      <c r="H1" s="5">
+      <c r="I1" s="5">
         <v>2027</v>
       </c>
-      <c r="I1" s="5">
+      <c r="J1" s="5">
         <v>2028</v>
       </c>
-      <c r="J1" s="5">
+      <c r="K1" s="5">
         <v>2029</v>
       </c>
-      <c r="K1" s="5">
+      <c r="L1" s="5">
         <v>2030</v>
       </c>
-      <c r="L1" s="5">
+      <c r="M1" s="5">
         <v>2031</v>
       </c>
-      <c r="M1" s="5">
+      <c r="N1" s="5">
         <v>2032</v>
       </c>
-      <c r="N1" s="5">
+      <c r="O1" s="5">
         <v>2033</v>
       </c>
-      <c r="O1" s="5">
+      <c r="P1" s="5">
         <v>2034</v>
       </c>
-      <c r="P1" s="5">
+      <c r="Q1" s="5">
         <v>2035</v>
       </c>
-      <c r="Q1" s="5">
+      <c r="R1" s="5">
         <v>2036</v>
       </c>
-      <c r="R1" s="5">
+      <c r="S1" s="5">
         <v>2037</v>
       </c>
-      <c r="S1" s="5">
+      <c r="T1" s="5">
         <v>2038</v>
       </c>
-      <c r="T1" s="5">
+      <c r="U1" s="5">
         <v>2039</v>
       </c>
-      <c r="U1" s="5">
+      <c r="V1" s="5">
         <v>2040</v>
       </c>
-      <c r="V1" s="5">
+      <c r="W1" s="5">
         <v>2041</v>
       </c>
-      <c r="W1" s="5">
+      <c r="X1" s="5">
         <v>2042</v>
       </c>
-      <c r="X1" s="5">
+      <c r="Y1" s="5">
         <v>2043</v>
       </c>
-      <c r="Y1" s="5">
+      <c r="Z1" s="5">
         <v>2044</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="AA1" s="5">
         <v>2045</v>
       </c>
-      <c r="AA1" s="5">
+      <c r="AB1" s="5">
         <v>2046</v>
       </c>
-      <c r="AB1" s="5">
+      <c r="AC1" s="5">
         <v>2047</v>
       </c>
-      <c r="AC1" s="5">
+      <c r="AD1" s="5">
         <v>2048</v>
       </c>
-      <c r="AD1" s="5">
+      <c r="AE1" s="5">
         <v>2049</v>
       </c>
-      <c r="AE1" s="5">
+      <c r="AF1" s="5">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -911,8 +914,11 @@
       <c r="AE2" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1006,8 +1012,11 @@
       <c r="AE3" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1101,8 +1110,11 @@
       <c r="AE4" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1196,8 +1208,11 @@
       <c r="AE5" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1291,8 +1306,11 @@
       <c r="AE6" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1386,8 +1404,11 @@
       <c r="AE7" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1419,7 +1440,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1451,7 +1472,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1483,7 +1504,7 @@
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1515,7 +1536,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1547,7 +1568,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1579,7 +1600,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1611,7 +1632,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1643,7 +1664,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -2005,21 +2026,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -2163,24 +2169,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42875609-79F9-4385-91A9-A0EB6ADA0E2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF84DB0A-3AEE-44AF-AA48-35691CCAFEB9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{420D6414-8A0A-45DE-AF69-5009ECF78DBA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2196,4 +2200,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF84DB0A-3AEE-44AF-AA48-35691CCAFEB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42875609-79F9-4385-91A9-A0EB6ADA0E2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>